--- a/data/messy_abstraction_workbook.xlsx
+++ b/data/messy_abstraction_workbook.xlsx
@@ -514,10 +514,8 @@
           <t>C0003</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1/13/15</t>
-        </is>
+      <c r="D5" s="1">
+        <v>42017</v>
       </c>
       <c r="E5">
         <v>68</v>
@@ -560,6 +558,11 @@
       <c r="O5">
         <v>90.6</v>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>revised 2024 for instability</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -590,8 +593,10 @@
           <t>F</t>
         </is>
       </c>
-      <c r="G6">
-        <v>30.6</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>30.6 kg/m2</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -613,22 +618,23 @@
           <t>1 day</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>January 21 2015</t>
-        </is>
+      <c r="L6" s="1">
+        <v>42025</v>
       </c>
       <c r="M6">
         <v>67.3</v>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2/10/16</t>
-        </is>
+      <c r="N6" s="1">
+        <v>42410</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>pt moved out of state</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -648,7 +654,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2/28/15</t>
+          <t>February 28 2015</t>
         </is>
       </c>
       <c r="E7">
@@ -698,7 +704,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>pt moved out of state</t>
+          <t>PROM by phone</t>
         </is>
       </c>
     </row>
@@ -723,10 +729,8 @@
           <t>2015-04-21</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>65 yo</t>
-        </is>
+      <c r="E8">
+        <v>65</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -756,10 +760,8 @@
           <t>0 (same day)</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>April 5 2015</t>
-        </is>
+      <c r="L8" s="1">
+        <v>42099</v>
       </c>
       <c r="M8">
         <v>39.7</v>
@@ -774,7 +776,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>check chart</t>
+          <t>PROM by phone</t>
         </is>
       </c>
     </row>
@@ -857,15 +859,11 @@
           <t>C0032</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5/13/15</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>68 yo</t>
-        </is>
+      <c r="D10" s="1">
+        <v>42137</v>
+      </c>
+      <c r="E10">
+        <v>68</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -895,23 +893,21 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2015-04-27</t>
+          <t>4/27/15</t>
         </is>
       </c>
       <c r="M10">
         <v>49</v>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>May 23 2016</t>
-        </is>
+      <c r="N10" s="1">
+        <v>42513</v>
       </c>
       <c r="O10">
         <v>74.5</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>pt moved out of state</t>
+          <t>check chart</t>
         </is>
       </c>
     </row>
@@ -931,10 +927,8 @@
           <t>C0037</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2015-06-18</t>
-        </is>
+      <c r="D11" s="1">
+        <v>42173</v>
       </c>
       <c r="E11">
         <v>63</v>
@@ -944,10 +938,8 @@
           <t>f</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>27.6 kg/m2</t>
-        </is>
+      <c r="G11">
+        <v>27.6</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -965,17 +957,15 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2015-05-25</t>
-        </is>
+      <c r="L11" s="1">
+        <v>42149</v>
       </c>
       <c r="M11">
         <v>43.3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2016-05-25</t>
+          <t>5/25/16</t>
         </is>
       </c>
       <c r="O11">
@@ -1003,10 +993,8 @@
           <t>C0043</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>July 18 2015</t>
-        </is>
+      <c r="D12" s="1">
+        <v>42203</v>
       </c>
       <c r="E12">
         <v>64</v>
@@ -1016,10 +1004,8 @@
           <t>f</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>30.0 kg/m2</t>
-        </is>
+      <c r="G12">
+        <v>30</v>
       </c>
       <c r="H12">
         <v>3</v>
@@ -1037,25 +1023,20 @@
       <c r="K12">
         <v>1</v>
       </c>
-      <c r="L12" s="1">
-        <v>42202</v>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2015-07-17</t>
+        </is>
       </c>
       <c r="M12">
         <v>44.6</v>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>6/20/16</t>
-        </is>
+      <c r="N12" s="1">
+        <v>42541</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>check chart</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1073,8 +1054,10 @@
           <t>C0049</t>
         </is>
       </c>
-      <c r="D13" s="1">
-        <v>42237</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2015-08-21</t>
+        </is>
       </c>
       <c r="E13">
         <v>54</v>
@@ -1084,10 +1067,8 @@
           <t>female</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>30.2 kg/m2</t>
-        </is>
+      <c r="G13">
+        <v>30.2</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -1115,7 +1096,17 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>pt moved out of state</t>
         </is>
       </c>
     </row>
@@ -1135,8 +1126,10 @@
           <t>C0051</t>
         </is>
       </c>
-      <c r="D14" s="1">
-        <v>42246</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>August 30 2015</t>
+        </is>
       </c>
       <c r="E14">
         <v>71</v>
@@ -1146,10 +1139,8 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>BMI 32.1</t>
-        </is>
+      <c r="G14">
+        <v>32.1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1171,25 +1162,21 @@
           <t>0 (same day)</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>August 16 2015</t>
-        </is>
+      <c r="L14" s="1">
+        <v>42232</v>
       </c>
       <c r="M14">
         <v>25.1</v>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>8/29/16</t>
-        </is>
+      <c r="N14" s="1">
+        <v>42611</v>
       </c>
       <c r="O14">
         <v>70.7</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>check chart</t>
+          <t>PROM by phone</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1198,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>March 3 2016</t>
+          <t>3/3/16</t>
         </is>
       </c>
       <c r="E15">
@@ -1241,8 +1228,10 @@
       <c r="K15">
         <v>2</v>
       </c>
-      <c r="L15" s="1">
-        <v>42409</v>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>February 9 2016</t>
+        </is>
       </c>
       <c r="M15">
         <v>35</v>
@@ -1253,11 +1242,6 @@
       <c r="O15">
         <v>74</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>check chart</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1307,27 +1291,18 @@
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>3/14/16</t>
-        </is>
+      <c r="L16" s="1">
+        <v>42443</v>
       </c>
       <c r="M16">
         <v>51.3</v>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2017-04-12</t>
-        </is>
+      <c r="N16" s="1">
+        <v>42837</v>
       </c>
       <c r="O16">
         <v>100</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>PROM by phone</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1358,10 +1333,8 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>BMI 29.1</t>
-        </is>
+      <c r="G17">
+        <v>29.1</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -1381,25 +1354,18 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>April 29 2016</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="M17">
         <v>35.5</v>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>5/3/17</t>
-        </is>
+      <c r="N17" s="1">
+        <v>42858</v>
       </c>
       <c r="O17">
         <v>61.6</v>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>pt moved out of state</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1417,8 +1383,10 @@
           <t>C0098</t>
         </is>
       </c>
-      <c r="D18" s="1">
-        <v>42516</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>May 26 2016</t>
+        </is>
       </c>
       <c r="E18">
         <v>70</v>
@@ -1430,31 +1398,33 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ASA 3</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>htn,dm</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Right TKA</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>999</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>ASA 3</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>htn,dm</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Right TKA</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="L18" s="1">
-        <v>42502</v>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>5/12/16</t>
+        </is>
       </c>
       <c r="M18">
         <v>36</v>
@@ -1466,12 +1436,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>unk</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>PROM by phone</t>
+          <t>999</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1458,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>June 3 2016</t>
+          <t>2016-06-03</t>
         </is>
       </c>
       <c r="E19">
@@ -1504,8 +1469,10 @@
           <t>F</t>
         </is>
       </c>
-      <c r="G19">
-        <v>27.4</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BMI 27.4</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1527,27 +1494,20 @@
           <t>0 (same day)</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2016-05-18</t>
-        </is>
+      <c r="L19" s="1">
+        <v>42508</v>
       </c>
       <c r="M19">
         <v>58.4</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>check chart</t>
         </is>
       </c>
     </row>
@@ -1578,8 +1538,10 @@
           <t>F</t>
         </is>
       </c>
-      <c r="G20">
-        <v>28.7</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>28.7 kg/m2</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1599,10 +1561,8 @@
       <c r="K20">
         <v>1</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2016-06-05</t>
-        </is>
+      <c r="L20" s="1">
+        <v>42526</v>
       </c>
       <c r="M20">
         <v>62.7</v>
@@ -1612,9 +1572,14 @@
           <t>N/A</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>check chart</t>
+          <t>revised 2022 for infection</t>
         </is>
       </c>
     </row>
@@ -1645,10 +1610,8 @@
           <t>f</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>33.4 kg/m2</t>
-        </is>
+      <c r="G21">
+        <v>33.4</v>
       </c>
       <c r="H21">
         <v>2</v>
@@ -1668,15 +1631,15 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6/24/16</t>
+          <t>June 24 2016</t>
         </is>
       </c>
       <c r="M21">
         <v>59.4</v>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>unk</t>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1731,14 +1694,18 @@
       <c r="K22">
         <v>0</v>
       </c>
-      <c r="L22" s="1">
-        <v>42555</v>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>July 4 2016</t>
+        </is>
       </c>
       <c r="M22">
         <v>40.9</v>
       </c>
-      <c r="N22" s="1">
-        <v>42953</v>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>August 6 2017</t>
+        </is>
       </c>
       <c r="O22">
         <v>100</v>
@@ -1760,10 +1727,8 @@
           <t>C0119</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2016-08-10</t>
-        </is>
+      <c r="D23" s="1">
+        <v>42592</v>
       </c>
       <c r="E23">
         <v>59</v>
@@ -1794,25 +1759,22 @@
           <t>0 (same day)</t>
         </is>
       </c>
-      <c r="L23" s="1">
-        <v>42587</v>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>August 5 2016</t>
+        </is>
       </c>
       <c r="M23">
         <v>49.8</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>August 11 2017</t>
+          <t>8/11/17</t>
         </is>
       </c>
       <c r="O23">
         <v>77.9</v>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>pt moved out of state</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1832,13 +1794,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>March 2 2017</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>80 yo</t>
-        </is>
+          <t>2017-03-02</t>
+        </is>
+      </c>
+      <c r="E24">
+        <v>80</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1882,7 +1842,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>pt moved out of state</t>
+          <t>check chart</t>
         </is>
       </c>
     </row>
@@ -1902,15 +1862,11 @@
           <t>C0205</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>11/2/17</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>58 yo</t>
-        </is>
+      <c r="D25" s="1">
+        <v>43041</v>
+      </c>
+      <c r="E25">
+        <v>58</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1936,14 +1892,21 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="L25" s="1">
-        <v>43018</v>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>October 10 2017</t>
+        </is>
       </c>
       <c r="M25">
         <v>33.5</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>unk</t>
         </is>
       </c>
@@ -1964,10 +1927,8 @@
           <t>C0209</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2017-11-08</t>
-        </is>
+      <c r="D26" s="1">
+        <v>43047</v>
       </c>
       <c r="E26">
         <v>70</v>
@@ -1977,10 +1938,8 @@
           <t>female</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>28.4 kg/m2</t>
-        </is>
+      <c r="G26">
+        <v>28.4</v>
       </c>
       <c r="H26">
         <v>2</v>
@@ -2000,17 +1959,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>October 30 2018</t>
+          <t>2018-10-30</t>
         </is>
       </c>
       <c r="O26">
@@ -2043,10 +2002,8 @@
           <t>11/24/17</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>78 yo</t>
-        </is>
+      <c r="E27">
+        <v>78</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2074,18 +2031,27 @@
           <t>0 days</t>
         </is>
       </c>
-      <c r="L27" s="1">
-        <v>43049</v>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>November 10 2017</t>
+        </is>
       </c>
       <c r="M27">
         <v>43.8</v>
       </c>
-      <c r="N27" s="1">
-        <v>43454</v>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>12/20/18</t>
+        </is>
       </c>
       <c r="O27">
         <v>86.4</v>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>pt moved out of state</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2105,7 +2071,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>December 6 2017</t>
+          <t>2017-12-06</t>
         </is>
       </c>
       <c r="E28">
@@ -2137,25 +2103,18 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2017-11-25</t>
+          <t>November 25 2017</t>
         </is>
       </c>
       <c r="M28">
         <v>37.9</v>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>November 18 2018</t>
-        </is>
+      <c r="N28" s="1">
+        <v>43422</v>
       </c>
       <c r="O28">
         <v>69.7</v>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>check chart</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2186,11 +2145,6 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>unk</t>
-        </is>
-      </c>
       <c r="H29">
         <v>1</v>
       </c>
@@ -2211,7 +2165,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2018-02-01</t>
+          <t>2/1/18</t>
         </is>
       </c>
       <c r="M29">
@@ -2219,7 +2173,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>February 21 2019</t>
         </is>
       </c>
       <c r="O29">
@@ -2227,7 +2181,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PROM by phone</t>
+          <t>pt moved out of state</t>
         </is>
       </c>
     </row>
@@ -2252,10 +2206,8 @@
           <t>2018-07-20</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>51 yo</t>
-        </is>
+      <c r="E30">
+        <v>51</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2264,7 +2216,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>39.4 kg/m2</t>
+          <t>BMI 39.4</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2285,12 +2237,19 @@
       <c r="K30">
         <v>1</v>
       </c>
-      <c r="L30" s="1">
-        <v>43287</v>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>July 6 2018</t>
+        </is>
       </c>
       <c r="M30">
         <v>35.6</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>999</t>
@@ -2318,10 +2277,8 @@
           <t>C0261</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2018-08-25</t>
-        </is>
+      <c r="D31" s="1">
+        <v>43337</v>
       </c>
       <c r="E31">
         <v>59</v>
@@ -2354,15 +2311,27 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t>unk</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N31" s="1">
-        <v>43702</v>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2019-08-25</t>
+        </is>
       </c>
       <c r="O31">
         <v>100</v>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>check chart</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2414,16 +2383,16 @@
       <c r="K32">
         <v>0</v>
       </c>
-      <c r="L32" s="1">
-        <v>43339</v>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>August 27 2018</t>
+        </is>
       </c>
       <c r="M32">
         <v>43.1</v>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2019-09-14</t>
-        </is>
+      <c r="N32" s="1">
+        <v>43722</v>
       </c>
       <c r="O32">
         <v>100</v>
@@ -2488,25 +2457,20 @@
           <t>0 (same day)</t>
         </is>
       </c>
-      <c r="L33" s="1">
-        <v>43376</v>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>10/3/18</t>
+        </is>
       </c>
       <c r="M33">
         <v>67.8</v>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2019-09-22</t>
-        </is>
+      <c r="N33" s="1">
+        <v>43730</v>
       </c>
       <c r="O33">
         <v>85.5</v>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>revised 2021 for instability</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2526,7 +2490,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>11/25/18</t>
+          <t>November 25 2018</t>
         </is>
       </c>
       <c r="E34">
@@ -2564,7 +2528,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>November 25 2019</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="O34">
@@ -2594,7 +2558,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>April 4 2019</t>
+          <t>2019-04-04</t>
         </is>
       </c>
       <c r="E35">
@@ -2607,7 +2571,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unk</t>
         </is>
       </c>
       <c r="H35">
@@ -2632,10 +2596,8 @@
       <c r="M35">
         <v>31.2</v>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>April 3 2020</t>
-        </is>
+      <c r="N35" s="1">
+        <v>43924</v>
       </c>
       <c r="O35">
         <v>73</v>
@@ -2659,11 +2621,13 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2019-05-14</t>
-        </is>
-      </c>
-      <c r="E36">
-        <v>62</v>
+          <t>May 14 2019</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>62 yo</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2697,11 +2661,6 @@
       <c r="M36">
         <v>54</v>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>unk</t>
@@ -2709,7 +2668,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>check chart</t>
+          <t>PROM by phone</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2690,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>June 1 2019</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="E37">
@@ -2761,25 +2720,22 @@
       <c r="K37">
         <v>1</v>
       </c>
-      <c r="L37" s="1">
-        <v>43603</v>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>May 18 2019</t>
+        </is>
       </c>
       <c r="M37">
         <v>58</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2020-05-31</t>
+          <t>May 31 2020</t>
         </is>
       </c>
       <c r="O37">
         <v>95.1</v>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>check chart</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2802,8 +2758,10 @@
           <t>2019-06-23</t>
         </is>
       </c>
-      <c r="E38">
-        <v>67</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>67 yo</t>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2825,23 +2783,22 @@
           <t>2 days</t>
         </is>
       </c>
-      <c r="L38" s="1">
-        <v>43623</v>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>6/7/19</t>
+        </is>
       </c>
       <c r="M38">
         <v>43.9</v>
       </c>
-      <c r="N38" s="1">
-        <v>44004</v>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2020-06-22</t>
+        </is>
       </c>
       <c r="O38">
         <v>89.9</v>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>PROM by phone</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2859,8 +2816,10 @@
           <t>C0320</t>
         </is>
       </c>
-      <c r="D39" s="1">
-        <v>43648</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>7/2/19</t>
+        </is>
       </c>
       <c r="E39">
         <v>68</v>
@@ -2893,25 +2852,27 @@
           <t>3 days</t>
         </is>
       </c>
-      <c r="L39" s="1">
-        <v>43633</v>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>6/17/19</t>
+        </is>
       </c>
       <c r="M39">
         <v>70.3</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
+          <t>unk</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PROM by phone</t>
+          <t>check chart</t>
         </is>
       </c>
     </row>
@@ -2931,8 +2892,10 @@
           <t>C0321</t>
         </is>
       </c>
-      <c r="D40" s="1">
-        <v>43650</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>July 4 2019</t>
+        </is>
       </c>
       <c r="E40">
         <v>62</v>
@@ -2963,16 +2926,16 @@
       <c r="K40">
         <v>5</v>
       </c>
-      <c r="L40" s="1">
-        <v>43637</v>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6/21/19</t>
+        </is>
       </c>
       <c r="M40">
         <v>25.2</v>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>2020-06-27</t>
-        </is>
+      <c r="N40" s="1">
+        <v>44009</v>
       </c>
       <c r="O40">
         <v>63.4</v>
@@ -3001,7 +2964,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>August 28 2019</t>
+          <t>8/28/19</t>
         </is>
       </c>
       <c r="E41">
@@ -3037,7 +3000,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>8/14/19</t>
+          <t>2019-08-14</t>
         </is>
       </c>
       <c r="M41">
@@ -3045,17 +3008,17 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>unk</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unk</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>revised 2020 for loosening</t>
+          <t>revised 2019 for loosening</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3040,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10/8/19</t>
+          <t>2019-10-08</t>
         </is>
       </c>
       <c r="E42">
@@ -3117,12 +3080,17 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>October 7 2020</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="O42">
         <v>85.3</v>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>PROM by phone</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3140,10 +3108,8 @@
           <t>C0345</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>10/26/19</t>
-        </is>
+      <c r="D43" s="1">
+        <v>43764</v>
       </c>
       <c r="E43">
         <v>70</v>
@@ -3174,22 +3140,20 @@
           <t>1 day</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>October 9 2019</t>
-        </is>
+      <c r="L43" s="1">
+        <v>43747</v>
       </c>
       <c r="M43">
         <v>60.9</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>999</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>revised 2021 for infection</t>
+          <t>revised 2020 for instability</t>
         </is>
       </c>
     </row>
@@ -3209,8 +3173,10 @@
           <t>C0362</t>
         </is>
       </c>
-      <c r="D44" s="1">
-        <v>43854</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1/24/20</t>
+        </is>
       </c>
       <c r="E44">
         <v>57</v>
@@ -3220,8 +3186,10 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G44">
-        <v>26.2</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>26.2 kg/m2</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3251,19 +3219,12 @@
       <c r="M44">
         <v>79.9</v>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>2021-02-02</t>
-        </is>
+      <c r="N44" s="1">
+        <v>44229</v>
       </c>
       <c r="O44">
         <v>100</v>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>pt moved out of state</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3283,7 +3244,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>February 10 2020</t>
+          <t>2020-02-10</t>
         </is>
       </c>
       <c r="E45">
@@ -3294,10 +3255,8 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>BMI 34.5</t>
-        </is>
+      <c r="G45">
+        <v>34.5</v>
       </c>
       <c r="H45">
         <v>2</v>
@@ -3325,7 +3284,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2/9/21</t>
+          <t>February 9 2021</t>
         </is>
       </c>
       <c r="O45">
@@ -3348,8 +3307,10 @@
           <t>C0366</t>
         </is>
       </c>
-      <c r="D46" s="1">
-        <v>43873</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>February 12 2020</t>
+        </is>
       </c>
       <c r="E46">
         <v>73</v>
@@ -3359,10 +3320,8 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>26.8 kg/m2</t>
-        </is>
+      <c r="G46">
+        <v>26.8</v>
       </c>
       <c r="H46">
         <v>3</v>
@@ -3380,8 +3339,10 @@
       <c r="K46">
         <v>3</v>
       </c>
-      <c r="L46" s="1">
-        <v>43847</v>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
       </c>
       <c r="M46">
         <v>48</v>
@@ -3396,7 +3357,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>revised 2020 for loosening</t>
+          <t>revised 2024 for infection</t>
         </is>
       </c>
     </row>
@@ -3416,10 +3377,8 @@
           <t>C0375</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>3/4/20</t>
-        </is>
+      <c r="D47" s="1">
+        <v>43894</v>
       </c>
       <c r="E47">
         <v>57</v>
@@ -3429,10 +3388,8 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>29.3 kg/m2</t>
-        </is>
+      <c r="G47">
+        <v>29.3</v>
       </c>
       <c r="H47">
         <v>2</v>
@@ -3452,7 +3409,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2020-02-19</t>
+          <t>2/19/20</t>
         </is>
       </c>
       <c r="M47">
@@ -3460,17 +3417,12 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
+          <t>unk</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>PROM by phone</t>
         </is>
       </c>
     </row>
@@ -3490,15 +3442,11 @@
           <t>C0376</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>March 19 2020</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>62 yo</t>
-        </is>
+      <c r="D48" s="1">
+        <v>43909</v>
+      </c>
+      <c r="E48">
+        <v>62</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3530,7 +3478,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>3/5/20</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="M48">
@@ -3538,17 +3486,12 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>unk</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>check chart</t>
+          <t>revised 2020 for infection</t>
         </is>
       </c>
     </row>
@@ -3573,8 +3516,10 @@
           <t>May 3 2020</t>
         </is>
       </c>
-      <c r="E49">
-        <v>73</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>73 yo</t>
+        </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3602,25 +3547,20 @@
           <t>0 (same day)</t>
         </is>
       </c>
-      <c r="L49" s="1">
-        <v>43953</v>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>May 2 2020</t>
+        </is>
       </c>
       <c r="M49">
         <v>62.4</v>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>May 31 2021</t>
-        </is>
+      <c r="N49" s="1">
+        <v>44347</v>
       </c>
       <c r="O49">
         <v>100</v>
       </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>check chart</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3638,23 +3578,21 @@
           <t>C0393</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2020-07-17</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>76 yo</t>
-        </is>
+      <c r="D50" s="1">
+        <v>44029</v>
+      </c>
+      <c r="E50">
+        <v>76</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>f</t>
         </is>
       </c>
-      <c r="G50">
-        <v>38.9</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>38.9 kg/m2</t>
+        </is>
       </c>
       <c r="H50">
         <v>3</v>
@@ -3674,23 +3612,20 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>July 3 2020</t>
+          <t>7/3/20</t>
         </is>
       </c>
       <c r="M50">
         <v>72.4</v>
       </c>
-      <c r="N50" s="1">
-        <v>44394</v>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2021-07-17</t>
+        </is>
       </c>
       <c r="O50">
         <v>82.1</v>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>check chart</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3710,7 +3645,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2020-11-15</t>
+          <t>11/15/20</t>
         </is>
       </c>
       <c r="E51">
@@ -3721,8 +3656,10 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G51">
-        <v>30.8</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>BMI 30.8</t>
+        </is>
       </c>
       <c r="H51">
         <v>3</v>
@@ -3758,6 +3695,11 @@
       <c r="O51">
         <v>80.8</v>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>pt moved out of state</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3775,13 +3717,13 @@
           <t>C0422</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>March 1 2021</t>
-        </is>
-      </c>
-      <c r="E52">
-        <v>63</v>
+      <c r="D52" s="1">
+        <v>44256</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>63 yo</t>
+        </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3817,15 +3759,17 @@
       <c r="M52">
         <v>46.8</v>
       </c>
-      <c r="N52" s="1">
-        <v>44609</v>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>February 17 2022</t>
+        </is>
       </c>
       <c r="O52">
         <v>80.8</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>PROM by phone</t>
+          <t>check chart</t>
         </is>
       </c>
     </row>
@@ -3847,21 +3791,21 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>68 yo</t>
-        </is>
+          <t>April 7 2021</t>
+        </is>
+      </c>
+      <c r="E53">
+        <v>68</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="G53">
-        <v>35.4</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>35.4 kg/m2</t>
+        </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3881,23 +3825,22 @@
       <c r="K53">
         <v>4</v>
       </c>
-      <c r="L53" s="1">
-        <v>44282</v>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2021-03-27</t>
+        </is>
       </c>
       <c r="M53">
         <v>42.4</v>
       </c>
-      <c r="N53" s="1">
-        <v>44680</v>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
       </c>
       <c r="O53">
         <v>86.5</v>
       </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>PROM by phone</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3918,8 +3861,10 @@
       <c r="D54" s="1">
         <v>44368</v>
       </c>
-      <c r="E54">
-        <v>71</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>71 yo</t>
+        </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3928,7 +3873,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>unk</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54">
@@ -3947,21 +3892,25 @@
       <c r="K54">
         <v>0</v>
       </c>
-      <c r="L54" s="1">
-        <v>44343</v>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2021-05-27</t>
+        </is>
       </c>
       <c r="M54">
         <v>41</v>
       </c>
-      <c r="N54" s="1">
-        <v>44733</v>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>6/21/22</t>
+        </is>
       </c>
       <c r="O54">
         <v>83.3</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>PROM by phone</t>
+          <t>pt moved out of state</t>
         </is>
       </c>
     </row>
@@ -3981,10 +3930,8 @@
           <t>C0462</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>November 2 2021</t>
-        </is>
+      <c r="D55" s="1">
+        <v>44502</v>
       </c>
       <c r="E55">
         <v>55</v>
@@ -3994,10 +3941,8 @@
           <t>female</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>BMI 37.6</t>
-        </is>
+      <c r="G55">
+        <v>37.6</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -4017,22 +3962,25 @@
       <c r="K55">
         <v>0</v>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>2021-10-12</t>
-        </is>
+      <c r="L55" s="1">
+        <v>44481</v>
       </c>
       <c r="M55">
         <v>52.6</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>November 2 2022</t>
+          <t>11/2/22</t>
         </is>
       </c>
       <c r="O55">
         <v>81.8</v>
       </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>pt moved out of state</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4050,10 +3998,8 @@
           <t>C0464</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2021-11-04</t>
-        </is>
+      <c r="D56" s="1">
+        <v>44504</v>
       </c>
       <c r="E56">
         <v>58</v>
@@ -4063,8 +4009,10 @@
           <t>female</t>
         </is>
       </c>
-      <c r="G56">
-        <v>32.3</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>BMI 32.3</t>
+        </is>
       </c>
       <c r="H56">
         <v>2</v>
@@ -4095,12 +4043,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>999</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>pt moved out of state</t>
+          <t>check chart</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4070,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>11/27/21</t>
+          <t>2021-11-27</t>
         </is>
       </c>
       <c r="E57">
@@ -4162,12 +4110,19 @@
       <c r="M57">
         <v>54.1</v>
       </c>
-      <c r="N57" s="1">
-        <v>44866</v>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
       </c>
       <c r="O57">
         <v>100</v>
       </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>revised 2025 for loosening</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4187,7 +4142,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2/10/22</t>
+          <t>February 10 2022</t>
         </is>
       </c>
       <c r="E58">
@@ -4221,23 +4176,23 @@
           <t>0 (same day)</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>January 27 2022</t>
-        </is>
+      <c r="L58" s="1">
+        <v>44588</v>
       </c>
       <c r="M58">
         <v>51</v>
       </c>
-      <c r="N58" s="1">
-        <v>44969</v>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2/12/23</t>
+        </is>
       </c>
       <c r="O58">
         <v>100</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>PROM by phone</t>
+          <t>check chart</t>
         </is>
       </c>
     </row>
@@ -4270,8 +4225,10 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G59">
-        <v>21.4</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>21.4 kg/m2</t>
+        </is>
       </c>
       <c r="H59">
         <v>3</v>
@@ -4291,125 +4248,123 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2022-04-30</t>
+          <t>4/30/22</t>
         </is>
       </c>
       <c r="M59">
         <v>61</v>
       </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>2023-06-06</t>
-        </is>
+      <c r="N59" s="1">
+        <v>45083</v>
       </c>
       <c r="O59">
         <v>95</v>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>check chart</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TESTPATIENT, KILO-037</t>
+          <t>TESTPATIENT, CHARLIE-030</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SYN-550925</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>C0043</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>July 18 2015</t>
-        </is>
+          <t>SYN-842878</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>C0345</t>
+        </is>
+      </c>
+      <c r="D60" s="1">
+        <v>43764</v>
       </c>
       <c r="E60">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>f</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>30.0 kg/m2</t>
-        </is>
+      <c r="G60">
+        <v>26</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>htn</t>
+          <t>HTN</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Total hip (L)</t>
-        </is>
-      </c>
-      <c r="K60">
-        <v>1</v>
+          <t>Total knee (L)</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1 day</t>
+        </is>
       </c>
       <c r="L60" s="1">
-        <v>42202</v>
+        <v>43747</v>
       </c>
       <c r="M60">
-        <v>44.6</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>6/20/16</t>
-        </is>
-      </c>
-      <c r="O60">
-        <v>100</v>
+        <v>60.9</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>check chart</t>
+          <t>revised 2020 for instability</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TESTPATIENT, BRAVO-005</t>
+          <t>TESTPATIENT, INDIA-013</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SYN-313772</t>
+          <t>SYN-187133</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>C0218</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>December 6 2017</t>
-        </is>
+          <t>C0261</t>
+        </is>
+      </c>
+      <c r="D61" s="1">
+        <v>43337</v>
       </c>
       <c r="E61">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>f</t>
         </is>
       </c>
       <c r="G61">
-        <v>45.7</v>
-      </c>
-      <c r="H61">
-        <v>3</v>
+        <v>30.8</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -4418,27 +4373,29 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>TKA (L)</t>
+          <t>Total knee (Left)</t>
         </is>
       </c>
       <c r="K61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2017-11-25</t>
-        </is>
-      </c>
-      <c r="M61">
-        <v>37.9</v>
+          <t>unk</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>November 18 2018</t>
+          <t>2019-08-25</t>
         </is>
       </c>
       <c r="O61">
-        <v>69.7</v>
+        <v>100</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -4464,13 +4421,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>August 19 2022</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>67 yo</t>
-        </is>
+          <t>2022-08-19</t>
+        </is>
+      </c>
+      <c r="E62">
+        <v>67</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -4500,7 +4455,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>8/5/22</t>
+          <t>August 5 2022</t>
         </is>
       </c>
       <c r="M62">
@@ -4514,6 +4469,11 @@
       <c r="O62">
         <v>80.6</v>
       </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>PROM by phone</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4536,10 +4496,8 @@
           <t>4/23/23</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>61 yo</t>
-        </is>
+      <c r="E63">
+        <v>61</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -4567,17 +4525,15 @@
       <c r="K63">
         <v>3</v>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>3/31/23</t>
-        </is>
+      <c r="L63" s="1">
+        <v>45016</v>
       </c>
       <c r="M63">
         <v>18.7</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>April 16 2024</t>
+          <t>4/16/24</t>
         </is>
       </c>
       <c r="O63">
@@ -4607,7 +4563,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2023-05-07</t>
+          <t>May 7 2023</t>
         </is>
       </c>
       <c r="E64">
@@ -4653,6 +4609,11 @@
       <c r="O64">
         <v>100</v>
       </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>PROM by phone</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4672,7 +4633,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5/11/23</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="E65">
@@ -4706,7 +4667,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>4/14/23</t>
+          <t>2023-04-14</t>
         </is>
       </c>
       <c r="M65">
@@ -4720,6 +4681,11 @@
       <c r="O65">
         <v>78.8</v>
       </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>check chart</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4739,7 +4705,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>12/14/23</t>
+          <t>2023-12-14</t>
         </is>
       </c>
       <c r="E66">
@@ -4775,7 +4741,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>November 30 2023</t>
+          <t>11/30/23</t>
         </is>
       </c>
       <c r="M66">
@@ -4789,7 +4755,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>PROM by phone</t>
+          <t>check chart</t>
         </is>
       </c>
     </row>
@@ -4974,50 +4940,47 @@
           <t>May 1 2015</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>75 yo</t>
-        </is>
+      <c r="E5">
+        <v>75</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="G5">
-        <v>26.9</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>26.9 kg/m2</t>
+        </is>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HTN</t>
+          <t>htn</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Total knee (R)</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2 days</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M5" s="1">
-        <v>42111</v>
+          <t>Right TKA</t>
+        </is>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4/17/15</t>
+        </is>
       </c>
       <c r="N5">
         <v>40.9</v>
       </c>
-      <c r="O5" s="1">
-        <v>42464</v>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2016-04-04</t>
+        </is>
       </c>
       <c r="P5">
         <v>92.5</v>
@@ -5044,17 +5007,15 @@
           <t>C0045</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7/30/15</t>
-        </is>
+      <c r="D6" s="1">
+        <v>42215</v>
       </c>
       <c r="E6">
         <v>55</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G6">
@@ -5065,7 +5026,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -5075,13 +5036,16 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0 (same day)</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>7/16/15</t>
-        </is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M6" s="1">
+        <v>42201</v>
       </c>
       <c r="N6">
         <v>36.5</v>
@@ -5111,49 +5075,45 @@
           <t>C0053</t>
         </is>
       </c>
-      <c r="D7" s="1">
-        <v>42255</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2015-09-08</t>
+        </is>
       </c>
       <c r="E7">
         <v>69</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="G7">
         <v>18.3</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
+      <c r="H7">
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DM and HTN</t>
+          <t>dm and htn</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>L TKA</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0 (same day)</t>
-        </is>
+          <t>L Total knee</t>
+        </is>
+      </c>
+      <c r="K7">
+        <v>0</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>8/25/15</t>
-        </is>
+      <c r="M7" s="1">
+        <v>42241</v>
       </c>
       <c r="N7">
         <v>59.1</v>
@@ -5168,7 +5128,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>pt moved out of state</t>
+          <t>check chart</t>
         </is>
       </c>
     </row>
@@ -5188,15 +5148,17 @@
           <t>C0060</t>
         </is>
       </c>
-      <c r="D8" s="1">
-        <v>42305</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10/28/15</t>
+        </is>
       </c>
       <c r="E8">
         <v>64</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>male</t>
         </is>
       </c>
       <c r="G8">
@@ -5217,18 +5179,18 @@
           <t>Right THA</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0 (same day)</t>
-        </is>
+      <c r="K8">
+        <v>0</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M8" s="1">
-        <v>42279</v>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2015-10-02</t>
+        </is>
       </c>
       <c r="N8">
         <v>47.1</v>
@@ -5258,7 +5220,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>November 1 2015</t>
+          <t>2015-11-01</t>
         </is>
       </c>
       <c r="E9">
@@ -5277,12 +5239,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GERD,HTN</t>
+          <t>htn</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>TKA (R)</t>
+          <t>R Total knee</t>
         </is>
       </c>
       <c r="K9">
@@ -5295,25 +5257,18 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10/20/15</t>
+          <t>2015-10-20</t>
         </is>
       </c>
       <c r="N9">
         <v>44.2</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>October 31 2016</t>
-        </is>
+      <c r="O9" s="1">
+        <v>42674</v>
       </c>
       <c r="P9">
         <v>94.9</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>PROM by phone</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5331,8 +5286,10 @@
           <t>C0064</t>
         </is>
       </c>
-      <c r="D10" s="1">
-        <v>42316</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2015-11-08</t>
+        </is>
       </c>
       <c r="E10">
         <v>56</v>
@@ -5350,12 +5307,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Nil</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Right Total knee</t>
+          <t>Right TKA</t>
         </is>
       </c>
       <c r="K10">
@@ -5363,12 +5320,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>12/1/16</t>
         </is>
       </c>
       <c r="P10">
@@ -5376,7 +5333,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>check chart</t>
+          <t>pt moved out of state</t>
         </is>
       </c>
     </row>
@@ -5396,26 +5353,24 @@
           <t>C0065</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>November 10 2015</t>
-        </is>
+      <c r="D11" s="1">
+        <v>42318</v>
       </c>
       <c r="E11">
         <v>51</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>BMI 31.6</t>
-        </is>
-      </c>
-      <c r="H11">
-        <v>2</v>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>31.6</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -5424,24 +5379,35 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Left THA</t>
-        </is>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="M11" s="1">
-        <v>42292</v>
+          <t>Total hip (L)</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1 day</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2015-10-15</t>
+        </is>
       </c>
       <c r="N11">
         <v>45.7</v>
       </c>
-      <c r="O11" s="1">
-        <v>42696</v>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>November 22 2016</t>
+        </is>
       </c>
       <c r="P11">
         <v>96.7</v>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>pt moved out of state</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5461,7 +5427,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12/29/15</t>
+          <t>December 29 2015</t>
         </is>
       </c>
       <c r="E12">
@@ -5469,13 +5435,11 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>33.3 kg/m2</t>
-        </is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>33.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -5489,18 +5453,11 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Right Total knee</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1 day</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+          <t>Total knee (Right)</t>
+        </is>
+      </c>
+      <c r="K12">
+        <v>1</v>
       </c>
       <c r="M12" s="1">
         <v>42354</v>
@@ -5508,12 +5465,19 @@
       <c r="N12">
         <v>44.1</v>
       </c>
-      <c r="O12" s="1">
-        <v>42732</v>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2016-12-28</t>
+        </is>
       </c>
       <c r="P12">
         <v>89.4</v>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>PROM by phone</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5531,15 +5495,19 @@
           <t>C0073</t>
         </is>
       </c>
-      <c r="D13" s="1">
-        <v>42376</v>
-      </c>
-      <c r="E13">
-        <v>77</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2016-01-07</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>77 yo</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>male</t>
         </is>
       </c>
       <c r="G13">
@@ -5550,7 +5518,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>osa,htn</t>
+          <t>OSA; HTN</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -5561,25 +5529,20 @@
       <c r="K13">
         <v>4</v>
       </c>
-      <c r="M13" s="1">
-        <v>42362</v>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>12/24/15</t>
+        </is>
       </c>
       <c r="N13">
         <v>31.6</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1/15/17</t>
-        </is>
+      <c r="O13" s="1">
+        <v>42750</v>
       </c>
       <c r="P13">
         <v>85.8</v>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>check chart</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5605,13 +5568,11 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>19.3 kg/m2</t>
-        </is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>19.3</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -5620,33 +5581,26 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nil</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Left THA</t>
+          <t>THA (L)</t>
         </is>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2016-02-22</t>
-        </is>
+      <c r="M14" s="1">
+        <v>42422</v>
       </c>
       <c r="N14">
         <v>52.2</v>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>999</t>
         </is>
       </c>
     </row>
@@ -5666,8 +5620,10 @@
           <t>C0089</t>
         </is>
       </c>
-      <c r="D15" s="1">
-        <v>42487</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2016-04-27</t>
+        </is>
       </c>
       <c r="E15">
         <v>61</v>
@@ -5685,7 +5641,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>HTN,hypothyroid</t>
+          <t>HTN</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -5703,7 +5659,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>April 17 2016</t>
+          <t>4/17/16</t>
         </is>
       </c>
       <c r="N15">
@@ -5714,11 +5670,6 @@
           <t>unk</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5749,13 +5700,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
+          <t>unk</t>
+        </is>
+      </c>
+      <c r="H16">
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -5764,29 +5713,27 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Right Total hip</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0 (same day)</t>
-        </is>
+          <t>R Total hip</t>
+        </is>
+      </c>
+      <c r="K16">
+        <v>0</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>4/8/16</t>
-        </is>
+      <c r="M16" s="1">
+        <v>42468</v>
       </c>
       <c r="N16">
         <v>49.6</v>
       </c>
-      <c r="O16" s="1">
-        <v>42853</v>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2017-04-28</t>
+        </is>
       </c>
       <c r="P16">
         <v>81.2</v>
@@ -5818,12 +5765,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BMI 34.9</t>
+          <t>34.9 kg/m2</t>
         </is>
       </c>
       <c r="H17">
@@ -5836,11 +5783,13 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Total hip (Right)</t>
-        </is>
-      </c>
-      <c r="K17">
-        <v>0</v>
+          <t>Right THA</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0 (same day)</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -5855,7 +5804,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>May 2 2017</t>
+          <t>2017-05-02</t>
         </is>
       </c>
       <c r="P17">
@@ -5886,25 +5835,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>BMI 38.8</t>
-        </is>
-      </c>
-      <c r="H18">
-        <v>3</v>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>38.8</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Nil</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Left Total knee</t>
+          <t>TKA (L)</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5914,24 +5863,28 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M18" s="1">
-        <v>42470</v>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2016-04-10</t>
+        </is>
       </c>
       <c r="N18">
         <v>36.4</v>
       </c>
-      <c r="O18" s="1">
-        <v>42829</v>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2017-04-04</t>
+        </is>
       </c>
       <c r="P18">
         <v>87.4</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>check chart</t>
+          <t>PROM by phone</t>
         </is>
       </c>
     </row>
@@ -5953,7 +5906,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6/27/16</t>
+          <t>June 27 2016</t>
         </is>
       </c>
       <c r="E19">
@@ -5961,11 +5914,13 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G19">
-        <v>26.8</v>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>BMI 26.8</t>
+        </is>
       </c>
       <c r="H19">
         <v>3</v>
@@ -5977,7 +5932,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Left Total hip</t>
+          <t>L Total hip</t>
         </is>
       </c>
       <c r="K19">
@@ -5985,7 +5940,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -5996,15 +5951,17 @@
       <c r="N19">
         <v>38.6</v>
       </c>
-      <c r="O19" s="1">
-        <v>42914</v>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
       </c>
       <c r="P19">
         <v>93.8</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>pt moved out of state</t>
+          <t>PROM by phone</t>
         </is>
       </c>
     </row>
@@ -6024,8 +5981,10 @@
           <t>C0109</t>
         </is>
       </c>
-      <c r="D20" s="1">
-        <v>42551</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2016-06-30</t>
+        </is>
       </c>
       <c r="E20">
         <v>64</v>
@@ -6053,26 +6012,24 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>unk</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>June 6 2016</t>
+          <t>6/6/16</t>
         </is>
       </c>
       <c r="N20">
         <v>63.4</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>June 30 2017</t>
-        </is>
+      <c r="O20" s="1">
+        <v>42916</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -6106,7 +6063,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6121,25 +6078,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Total hip (Left)</t>
-        </is>
-      </c>
-      <c r="K21">
-        <v>0</v>
+          <t>L THA</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0 (same day)</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
+          <t>7/12/16</t>
         </is>
       </c>
       <c r="N21">
@@ -6147,12 +6106,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>7/26/17</t>
+          <t>July 26 2017</t>
         </is>
       </c>
       <c r="P21">
         <v>61.1</v>
       </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>pt moved out of state</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6170,17 +6134,15 @@
           <t>C0116</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>August 8 2016</t>
-        </is>
+      <c r="D22" s="1">
+        <v>42590</v>
       </c>
       <c r="E22">
         <v>59</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6193,12 +6155,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>HTN</t>
+          <t>HTN and GERD</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Right Total hip</t>
+          <t>THA (R)</t>
         </is>
       </c>
       <c r="K22">
@@ -6206,23 +6168,25 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M22" s="1">
-        <v>42573</v>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2016-07-22</t>
+        </is>
       </c>
       <c r="N22">
         <v>40.8</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>check chart</t>
         </is>
       </c>
     </row>
@@ -6242,26 +6206,24 @@
           <t>C0121</t>
         </is>
       </c>
-      <c r="D23" s="1">
-        <v>42599</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8/17/16</t>
+        </is>
       </c>
       <c r="E23">
         <v>51</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>31.3 kg/m2</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>ASA 2</t>
-        </is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>31.3</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -6270,17 +6232,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>R Total hip</t>
+          <t>Right THA</t>
         </is>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>2016-07-23</t>
@@ -6297,6 +6254,11 @@
       <c r="P23">
         <v>100</v>
       </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>check chart</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6314,24 +6276,24 @@
           <t>C0124</t>
         </is>
       </c>
-      <c r="D24" s="1">
-        <v>42631</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>9/18/16</t>
+        </is>
       </c>
       <c r="E24">
         <v>52</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G24">
         <v>36.6</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
+      <c r="H24">
+        <v>2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -6340,33 +6302,33 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>TKA (Right)</t>
-        </is>
-      </c>
-      <c r="K24">
-        <v>0</v>
+          <t>Right TKA</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0 (same day)</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2016-09-04</t>
-        </is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M24" s="1">
+        <v>42617</v>
       </c>
       <c r="N24">
         <v>71.9</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>unk</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>unk</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6350,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10/16/16</t>
+          <t>October 16 2016</t>
         </is>
       </c>
       <c r="E25">
@@ -6396,7 +6358,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>male</t>
         </is>
       </c>
       <c r="G25">
@@ -6407,26 +6369,19 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>HTN</t>
+          <t>htn</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>TKA (Right)</t>
+          <t>R TKA</t>
         </is>
       </c>
       <c r="K25">
         <v>3</v>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2016-10-02</t>
-        </is>
+      <c r="M25" s="1">
+        <v>42645</v>
       </c>
       <c r="N25">
         <v>57.3</v>
@@ -6461,15 +6416,17 @@
           <t>C0143</t>
         </is>
       </c>
-      <c r="D26" s="1">
-        <v>42726</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>12/22/16</t>
+        </is>
       </c>
       <c r="E26">
         <v>69</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G26">
@@ -6477,12 +6434,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>999</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>HTN,DM</t>
+          <t>DM; HTN</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -6490,9 +6447,12 @@
           <t>Right Total knee</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0 (same day)</t>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -6503,14 +6463,19 @@
       <c r="N26">
         <v>18.3</v>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>unk</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>check chart</t>
+          <t>PROM by phone</t>
         </is>
       </c>
     </row>
@@ -6530,17 +6495,17 @@
           <t>C0151</t>
         </is>
       </c>
-      <c r="D27" s="1">
-        <v>42761</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>81 yo</t>
-        </is>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>January 26 2017</t>
+        </is>
+      </c>
+      <c r="E27">
+        <v>81</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G27">
@@ -6551,17 +6516,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>HTN</t>
+          <t>htn</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Left Total knee</t>
+          <t>TKA (Left)</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0 (same day)</t>
+          <t>0 days</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -6605,53 +6570,44 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>BMI 28.0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>28</v>
+      </c>
+      <c r="H28">
+        <v>3</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>htn</t>
+          <t>HTN</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Total hip (R)</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0 (same day)</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M28" s="1">
-        <v>42814</v>
+          <t>THA (Right)</t>
+        </is>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2017-03-20</t>
+        </is>
       </c>
       <c r="N28">
         <v>29.9</v>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>unk</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>check chart</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6629,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>April 14 2017</t>
+          <t>4/14/17</t>
         </is>
       </c>
       <c r="E29">
@@ -6681,27 +6637,31 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="G29">
-        <v>36</v>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>36.0 kg/m2</t>
+        </is>
       </c>
       <c r="H29">
         <v>3</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>DM; HTN</t>
+          <t>HTN; DM</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Total hip (Left)</t>
-        </is>
-      </c>
-      <c r="K29">
-        <v>3</v>
+          <t>THA (Left)</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>3 days</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -6710,25 +6670,23 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>April 14 2018</t>
-        </is>
+      <c r="O29" s="1">
+        <v>43204</v>
       </c>
       <c r="P29">
         <v>100</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>check chart</t>
+          <t>PROM by phone</t>
         </is>
       </c>
     </row>
@@ -6748,8 +6706,10 @@
           <t>C0165</t>
         </is>
       </c>
-      <c r="D30" s="1">
-        <v>42847</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>April 22 2017</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -6758,12 +6718,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>BMI 21.8</t>
+          <t>21.8 kg/m2</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6773,38 +6733,38 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Nil</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Left TKA</t>
+          <t>Total knee (L)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0 days</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>April 7 2017</t>
-        </is>
+          <t>0 (same day)</t>
+        </is>
+      </c>
+      <c r="M30" s="1">
+        <v>42832</v>
       </c>
       <c r="N30">
         <v>64.9</v>
       </c>
-      <c r="O30" s="1">
-        <v>43212</v>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>April 22 2018</t>
+        </is>
       </c>
       <c r="P30">
         <v>100</v>
       </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>PROM by phone</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6822,8 +6782,10 @@
           <t>C0169</t>
         </is>
       </c>
-      <c r="D31" s="1">
-        <v>42858</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>5/3/17</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -6840,27 +6802,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>ASA 2</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>dm</t>
+          <t>DM and hypothyroid</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Total hip (Left)</t>
+          <t>Total hip (L)</t>
         </is>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>April 19 2017</t>
@@ -6877,11 +6834,6 @@
       <c r="P31">
         <v>99.5</v>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>pt moved out of state</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6901,7 +6853,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6/3/17</t>
+          <t>June 3 2017</t>
         </is>
       </c>
       <c r="E32">
@@ -6912,15 +6864,11 @@
           <t>f</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>BMI 25.4</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
+      <c r="G32">
+        <v>25.4</v>
+      </c>
+      <c r="H32">
+        <v>2</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -6929,7 +6877,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>THA (Right)</t>
+          <t>Total hip (Right)</t>
         </is>
       </c>
       <c r="K32">
@@ -6937,7 +6885,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -6948,12 +6896,19 @@
       <c r="N32">
         <v>38.6</v>
       </c>
-      <c r="O32" s="1">
-        <v>43232</v>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>5/12/18</t>
+        </is>
       </c>
       <c r="P32">
         <v>69.8</v>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>pt moved out of state</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6971,19 +6926,15 @@
           <t>C0189</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>August 19 2017</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>75 yo</t>
-        </is>
+      <c r="D33" s="1">
+        <v>42966</v>
+      </c>
+      <c r="E33">
+        <v>75</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G33">
@@ -6999,11 +6950,13 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>R THA</t>
-        </is>
-      </c>
-      <c r="K33">
-        <v>0</v>
+          <t>R Total hip</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -7016,14 +6969,17 @@
       <c r="N33">
         <v>56.4</v>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2018-08-19</t>
-        </is>
+      <c r="O33" s="1">
+        <v>43331</v>
       </c>
       <c r="P33">
         <v>100</v>
       </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>PROM by phone</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7043,7 +6999,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8/20/17</t>
+          <t>2017-08-20</t>
         </is>
       </c>
       <c r="E34">
@@ -7054,8 +7010,10 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G34">
-        <v>32.1</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>BMI 32.1</t>
+        </is>
       </c>
       <c r="H34">
         <v>2</v>
@@ -7067,14 +7025,21 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>R THA</t>
+          <t>THA (R)</t>
         </is>
       </c>
       <c r="K34">
         <v>3</v>
       </c>
-      <c r="M34" s="1">
-        <v>42945</v>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2017-07-29</t>
+        </is>
       </c>
       <c r="N34">
         <v>31.7</v>
@@ -7085,11 +7050,6 @@
       <c r="P34">
         <v>94.3</v>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>pt moved out of state</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7107,39 +7067,40 @@
           <t>C0253</t>
         </is>
       </c>
-      <c r="D35" s="1">
-        <v>43299</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2018-07-18</t>
+        </is>
       </c>
       <c r="E35">
         <v>55</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>f</t>
         </is>
       </c>
       <c r="G35">
         <v>33</v>
       </c>
-      <c r="H35">
-        <v>2</v>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>OSA and DM</t>
+          <t>DM; OSA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Total knee (Right)</t>
-        </is>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>R TKA</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0 (same day)</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -7150,17 +7111,15 @@
       <c r="N35">
         <v>63.6</v>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>2019-07-18</t>
-        </is>
+      <c r="O35" s="1">
+        <v>43664</v>
       </c>
       <c r="P35">
         <v>81</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>revised 2020 for loosening</t>
+          <t>revised 2024 for infection</t>
         </is>
       </c>
     </row>
@@ -7180,15 +7139,17 @@
           <t>C0281</t>
         </is>
       </c>
-      <c r="D36" s="1">
-        <v>43473</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1/8/19</t>
+        </is>
       </c>
       <c r="E36">
         <v>75</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G36">
@@ -7204,27 +7165,31 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>TKA (L)</t>
-        </is>
-      </c>
-      <c r="K36">
-        <v>3</v>
+          <t>TKA (Left)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>3 days</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>December 14 2018</t>
+          <t>12/14/18</t>
         </is>
       </c>
       <c r="N36">
         <v>50.9</v>
       </c>
-      <c r="O36" s="1">
-        <v>43838</v>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2020-01-08</t>
+        </is>
       </c>
       <c r="P36">
         <v>88.1</v>
@@ -7251,8 +7216,10 @@
           <t>C0283</t>
         </is>
       </c>
-      <c r="D37" s="1">
-        <v>43477</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2019-01-12</t>
+        </is>
       </c>
       <c r="E37">
         <v>73</v>
@@ -7285,21 +7252,17 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2018-12-29</t>
-        </is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M37" s="1">
+        <v>43463</v>
       </c>
       <c r="N37">
         <v>46.2</v>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>January 12 2020</t>
-        </is>
+      <c r="O37" s="1">
+        <v>43842</v>
       </c>
       <c r="P37">
         <v>82.2</v>
@@ -7321,51 +7284,40 @@
           <t>C0284</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>January 14 2019</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>84 yo</t>
-        </is>
+      <c r="D38" s="1">
+        <v>43479</v>
+      </c>
+      <c r="E38">
+        <v>84</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>BMI 25.4</t>
-        </is>
-      </c>
-      <c r="H38">
-        <v>3</v>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G38">
+        <v>25.4</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ASA 3</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>DM; OA hands</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Right THA</t>
+          <t>Total hip (Right)</t>
         </is>
       </c>
       <c r="K38">
         <v>4</v>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>12/20/18</t>
-        </is>
+      <c r="M38" s="1">
+        <v>43454</v>
       </c>
       <c r="N38">
         <v>53.8</v>
@@ -7398,19 +7350,15 @@
           <t>C0290</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2019-02-06</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>69 yo</t>
-        </is>
+      <c r="D39" s="1">
+        <v>43502</v>
+      </c>
+      <c r="E39">
+        <v>69</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>female</t>
         </is>
       </c>
       <c r="G39">
@@ -7426,21 +7374,21 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>L Total hip</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>1 day</t>
-        </is>
+          <t>L THA</t>
+        </is>
+      </c>
+      <c r="K39">
+        <v>1</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M39" s="1">
-        <v>43497</v>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2019-02-01</t>
+        </is>
       </c>
       <c r="N39">
         <v>45.9</v>
@@ -7453,7 +7401,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>PROM by phone</t>
+          <t>check chart</t>
         </is>
       </c>
     </row>
@@ -7475,7 +7423,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>May 3 2019</t>
+          <t>2019-05-03</t>
         </is>
       </c>
       <c r="E40">
@@ -7483,7 +7431,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G40">
@@ -7494,7 +7442,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Nil</t>
+          <t>hypothyroid</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -7502,33 +7450,27 @@
           <t>TKA (Left)</t>
         </is>
       </c>
-      <c r="K40">
-        <v>1</v>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1 day</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M40" s="1">
-        <v>43576</v>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>4/21/19</t>
+        </is>
       </c>
       <c r="N40">
         <v>59.2</v>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>unk</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>pt moved out of state</t>
         </is>
       </c>
     </row>
@@ -7556,25 +7498,23 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>BMI 29.6</t>
-        </is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="G41">
+        <v>29.6</v>
       </c>
       <c r="H41">
         <v>2</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>L Total hip</t>
+          <t>Left THA</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -7584,11 +7524,13 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M41" s="1">
-        <v>43578</v>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2019-04-23</t>
+        </is>
       </c>
       <c r="N41">
         <v>33.3</v>
@@ -7599,11 +7541,6 @@
       <c r="P41">
         <v>80.2</v>
       </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>pt moved out of state</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7626,21 +7563,21 @@
           <t>2019-12-18</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>64 yo</t>
-        </is>
+      <c r="E42">
+        <v>64</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G42">
         <v>31.5</v>
       </c>
-      <c r="H42">
-        <v>3</v>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -7649,7 +7586,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Total hip (Left)</t>
+          <t>THA (Left)</t>
         </is>
       </c>
       <c r="K42">
@@ -7657,13 +7594,11 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2019-12-05</t>
-        </is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M42" s="1">
+        <v>43804</v>
       </c>
       <c r="N42">
         <v>39.7</v>
@@ -7699,28 +7634,30 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="G43">
-        <v>32.9</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>32.9 kg/m2</t>
+        </is>
       </c>
       <c r="H43">
         <v>2</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Nil</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Left Total knee</t>
+          <t>Total knee (Left)</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0 days</t>
+          <t>0 (same day)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -7736,7 +7673,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>3/2/21</t>
+          <t>March 2 2021</t>
         </is>
       </c>
       <c r="P43">
@@ -7761,7 +7698,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2/13/20</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="E44">
@@ -7775,33 +7712,40 @@
       <c r="G44">
         <v>24.4</v>
       </c>
-      <c r="H44">
-        <v>2</v>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ASA 2</t>
+        </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Right TKA</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>0 (same day)</t>
-        </is>
-      </c>
-      <c r="M44" s="1">
-        <v>43866</v>
+          <t>R TKA</t>
+        </is>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2020-02-05</t>
+        </is>
       </c>
       <c r="N44">
         <v>46.7</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>January 31 2021</t>
+          <t>1/31/21</t>
         </is>
       </c>
       <c r="P44">
@@ -7837,18 +7781,20 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G45">
-        <v>28.2</v>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>28.2 kg/m2</t>
+        </is>
       </c>
       <c r="H45">
         <v>2</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>htn,hypothyroid</t>
+          <t>HTN</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -7858,7 +7804,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>999</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -7866,20 +7812,22 @@
           <t>N</t>
         </is>
       </c>
-      <c r="M45" s="1">
-        <v>43881</v>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2/20/20</t>
+        </is>
       </c>
       <c r="N45">
         <v>57</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>unk</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -7899,10 +7847,8 @@
           <t>C0387</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2020-06-04</t>
-        </is>
+      <c r="D46" s="1">
+        <v>43986</v>
       </c>
       <c r="E46">
         <v>70</v>
@@ -7915,41 +7861,40 @@
       <c r="G46">
         <v>28.1</v>
       </c>
-      <c r="H46">
-        <v>2</v>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Left Total hip</t>
+          <t>THA (Left)</t>
         </is>
       </c>
       <c r="K46">
         <v>1</v>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M46" s="1">
-        <v>43970</v>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>May 19 2020</t>
+        </is>
       </c>
       <c r="N46">
         <v>61.1</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>revised 2024 for loosening</t>
+          <t>pt moved out of state</t>
         </is>
       </c>
     </row>
@@ -7979,25 +7924,27 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>BMI 28.0</t>
-        </is>
-      </c>
-      <c r="H47">
-        <v>1</v>
+          <t>28.0 kg/m2</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ASA 1</t>
+        </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Nil</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>THA (Left)</t>
+          <t>Left Total hip</t>
         </is>
       </c>
       <c r="K47">
@@ -8011,12 +7958,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>unk</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>unk</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>revised 2021 for infection</t>
         </is>
       </c>
     </row>
@@ -8052,27 +8004,24 @@
       <c r="G48">
         <v>20.4</v>
       </c>
-      <c r="H48">
-        <v>2</v>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Nil</t>
+          <t>GERD</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>R TKA</t>
+          <t>Right Total knee</t>
         </is>
       </c>
       <c r="K48">
         <v>5</v>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="M48" s="1">
         <v>44159</v>
       </c>
@@ -8081,12 +8030,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2021-12-04</t>
+          <t>12/4/21</t>
         </is>
       </c>
       <c r="P48">
         <v>81.2</v>
       </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>pt moved out of state</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8106,7 +8060,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>4/2/21</t>
+          <t>April 2 2021</t>
         </is>
       </c>
       <c r="E49">
@@ -8114,33 +8068,33 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G49">
         <v>29.8</v>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
+      <c r="H49">
+        <v>2</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>TKA (Left)</t>
-        </is>
-      </c>
-      <c r="K49">
-        <v>0</v>
+          <t>Left Total knee</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0 (same day)</t>
+        </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>March 14 2021</t>
+          <t>3/14/21</t>
         </is>
       </c>
       <c r="N49">
@@ -8148,12 +8102,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>unk</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>unk</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>pt moved out of state</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8134,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2021-11-19</t>
+          <t>11/19/21</t>
         </is>
       </c>
       <c r="E50">
@@ -8183,23 +8142,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G50">
         <v>44</v>
       </c>
-      <c r="H50">
-        <v>3</v>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>HTN; DM</t>
+          <t>HTN, DM</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>L TKA</t>
+          <t>Total knee (Left)</t>
         </is>
       </c>
       <c r="K50">
@@ -8207,12 +8168,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>11/14/21</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="N50">
@@ -8226,7 +8187,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>PROM by phone</t>
+          <t>check chart</t>
         </is>
       </c>
     </row>
@@ -8246,8 +8207,10 @@
           <t>C0472</t>
         </is>
       </c>
-      <c r="D51" s="1">
-        <v>44530</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2021-11-30</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -8262,17 +8225,19 @@
       <c r="G51">
         <v>24.1</v>
       </c>
-      <c r="H51">
-        <v>2</v>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>DM,HTN</t>
+          <t>DM; HTN</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>R TKA</t>
+          <t>Right Total knee</t>
         </is>
       </c>
       <c r="K51">
@@ -8285,7 +8250,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2021-11-18</t>
+          <t>11/18/21</t>
         </is>
       </c>
       <c r="N51">
@@ -8297,6 +8262,11 @@
       <c r="P51">
         <v>100</v>
       </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>PROM by phone</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8322,14 +8292,18 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="G52">
-        <v>32.1</v>
-      </c>
-      <c r="H52">
-        <v>3</v>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>BMI 32.1</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ASA 3</t>
+        </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -8338,7 +8312,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Left THA</t>
+          <t>Total hip (Left)</t>
         </is>
       </c>
       <c r="K52">
@@ -8349,17 +8323,15 @@
           <t>N</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>12/6/21</t>
-        </is>
+      <c r="M52" s="1">
+        <v>44536</v>
       </c>
       <c r="N52">
         <v>50.5</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>January 14 2023</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="P52">
@@ -8403,16 +8375,18 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>osa; htn</t>
+          <t>HTN and OSA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Right TKA</t>
-        </is>
-      </c>
-      <c r="K53">
-        <v>0</v>
+          <t>Right Total knee</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0 (same day)</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -8427,17 +8401,14 @@
       <c r="N53">
         <v>64.9</v>
       </c>
-      <c r="O53" s="1">
-        <v>44982</v>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2023-02-25</t>
+        </is>
       </c>
       <c r="P53">
         <v>98.1</v>
       </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>pt moved out of state</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8463,52 +8434,50 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="G54">
-        <v>35.2</v>
-      </c>
-      <c r="H54">
-        <v>2</v>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>35.2 kg/m2</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Nil</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>THA (Right)</t>
-        </is>
-      </c>
-      <c r="K54">
-        <v>0</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M54" s="1">
-        <v>44660</v>
+          <t>Total hip (Right)</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0 (same day)</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>April 9 2022</t>
+        </is>
       </c>
       <c r="N54">
         <v>44.3</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>April 23 2023</t>
+          <t>4/23/23</t>
         </is>
       </c>
       <c r="P54">
         <v>95.6</v>
       </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>check chart</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8526,25 +8495,25 @@
           <t>C0506</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2022-06-10</t>
-        </is>
+      <c r="D55" s="1">
+        <v>44722</v>
       </c>
       <c r="E55">
         <v>67</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G55">
-        <v>25.8</v>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>25.8 kg/m2</t>
+        </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>ASA 2</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -8554,7 +8523,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Total knee (Right)</t>
+          <t>Right Total knee</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -8567,17 +8536,20 @@
           <t>N</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>2022-05-17</t>
-        </is>
+      <c r="M55" s="1">
+        <v>44698</v>
       </c>
       <c r="N55">
         <v>43.4</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8599,21 +8571,21 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>June 21 2022</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>68 yo</t>
-        </is>
+          <t>2022-06-21</t>
+        </is>
+      </c>
+      <c r="E56">
+        <v>68</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G56">
-        <v>35.6</v>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>BMI 35.6</t>
+        </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -8622,12 +8594,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>htn; oa hands</t>
+          <t>OA hands,HTN</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>THA (L)</t>
+          <t>Left Total hip</t>
         </is>
       </c>
       <c r="K56">
@@ -8635,20 +8607,25 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2022-06-07</t>
+          <t>6/7/22</t>
         </is>
       </c>
       <c r="N56">
         <v>51.7</v>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>revised 2023 for loosening</t>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8668,15 +8645,17 @@
           <t>C0510</t>
         </is>
       </c>
-      <c r="D57" s="1">
-        <v>44761</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>7/19/22</t>
+        </is>
       </c>
       <c r="E57">
         <v>65</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G57">
@@ -8687,17 +8666,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Nil</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>L Total hip</t>
+          <t>Left THA</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0 (same day)</t>
+          <t>0 days</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -8715,7 +8694,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>unk</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>999</t>
         </is>
       </c>
     </row>
@@ -8735,10 +8719,8 @@
           <t>C0546</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>1/18/23</t>
-        </is>
+      <c r="D58" s="1">
+        <v>44944</v>
       </c>
       <c r="E58">
         <v>65</v>
@@ -8748,25 +8730,22 @@
           <t>M</t>
         </is>
       </c>
-      <c r="G58">
-        <v>22.4</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>BMI 22.4</t>
+        </is>
       </c>
       <c r="H58">
         <v>3</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>dm</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>THA (L)</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>unk</t>
+          <t>Total hip (Left)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -8782,17 +8761,14 @@
       <c r="N58">
         <v>53.5</v>
       </c>
-      <c r="O58" s="1">
-        <v>45302</v>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>1/11/24</t>
+        </is>
       </c>
       <c r="P58">
         <v>82.6</v>
       </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>check chart</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8810,35 +8786,33 @@
           <t>C0552</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>February 5 2023</t>
-        </is>
+      <c r="D59" s="1">
+        <v>44962</v>
       </c>
       <c r="E59">
         <v>62</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>33.5 kg/m2</t>
-        </is>
-      </c>
-      <c r="H59">
-        <v>2</v>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="G59">
+        <v>33.5</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>HTN</t>
+          <t>OA hands,HTN</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Total knee (R)</t>
+          <t>Right Total knee</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -8848,13 +8822,11 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>1/9/23</t>
-        </is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M59" s="1">
+        <v>44935</v>
       </c>
       <c r="N59">
         <v>48.1</v>
@@ -8867,31 +8839,36 @@
       <c r="P59">
         <v>69.5</v>
       </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>check chart</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TESTPATIENT, KILO-112</t>
+          <t>TESTPATIENT, HOTEL-091</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SYN-823968</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>C0029</t>
+          <t>SYN-680539</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>C0165</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>May 1 2015</t>
+          <t>April 22 2017</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>75 yo</t>
+          <t>66 yo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -8899,97 +8876,94 @@
           <t>male</t>
         </is>
       </c>
-      <c r="G60">
-        <v>26.9</v>
-      </c>
-      <c r="H60">
-        <v>2</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>21.8 kg/m2</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ASA 2</t>
+        </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>HTN</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Total knee (R)</t>
+          <t>Total knee (L)</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2 days</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>0 (same day)</t>
         </is>
       </c>
       <c r="M60" s="1">
-        <v>42111</v>
+        <v>42832</v>
       </c>
       <c r="N60">
-        <v>40.9</v>
-      </c>
-      <c r="O60" s="1">
-        <v>42464</v>
+        <v>64.9</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>April 22 2018</t>
+        </is>
       </c>
       <c r="P60">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>pt moved out of state</t>
+          <t>PROM by phone</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TESTPATIENT, ECHO-084</t>
+          <t>TESTPATIENT, ALPHA-120</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SYN-711916</t>
+          <t>SYN-469072</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>C0176</t>
+          <t>C0062</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>6/3/17</t>
+          <t>2015-11-01</t>
         </is>
       </c>
       <c r="E61">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>BMI 25.4</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G61">
+        <v>38.1</v>
+      </c>
+      <c r="H61">
+        <v>3</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>htn</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>THA (Right)</t>
+          <t>R Total knee</t>
         </is>
       </c>
       <c r="K61">
@@ -8997,22 +8971,22 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>5/14/17</t>
+          <t>2015-10-20</t>
         </is>
       </c>
       <c r="N61">
-        <v>38.6</v>
+        <v>44.2</v>
       </c>
       <c r="O61" s="1">
-        <v>43232</v>
+        <v>42674</v>
       </c>
       <c r="P61">
-        <v>69.8</v>
+        <v>94.9</v>
       </c>
     </row>
     <row r="62">
@@ -9033,7 +9007,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>April 27 2023</t>
+          <t>4/27/23</t>
         </is>
       </c>
       <c r="E62">
@@ -9041,13 +9015,11 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>BMI 26.9</t>
-        </is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="G62">
+        <v>26.9</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -9056,7 +9028,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>OA hands</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -9064,15 +9036,8 @@
           <t>R Total hip</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>0 (same day)</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+      <c r="K62">
+        <v>0</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -9082,14 +9047,17 @@
       <c r="N62">
         <v>36.5</v>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>2024-05-04</t>
-        </is>
+      <c r="O62" s="1">
+        <v>45416</v>
       </c>
       <c r="P62">
         <v>85.5</v>
       </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>PROM by phone</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9110,17 +9078,19 @@
       <c r="D63" s="1">
         <v>45088</v>
       </c>
-      <c r="E63">
-        <v>71</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>71 yo</t>
+        </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>BMI 34.3</t>
+          <t>34.3 kg/m2</t>
         </is>
       </c>
       <c r="H63">
@@ -9128,34 +9098,29 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Nil</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Right Total hip</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>2 days</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+          <t>THA (Right)</t>
+        </is>
+      </c>
+      <c r="K63">
+        <v>2</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
+          <t>6/4/23</t>
         </is>
       </c>
       <c r="N63">
         <v>52.4</v>
       </c>
-      <c r="O63" s="1">
-        <v>45471</v>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
       </c>
       <c r="P63">
         <v>63.5</v>
@@ -9177,26 +9142,22 @@
           <t>C0588</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>October 22 2023</t>
-        </is>
+      <c r="D64" s="1">
+        <v>45221</v>
       </c>
       <c r="E64">
         <v>69</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G64">
         <v>30</v>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>ASA 2</t>
-        </is>
+      <c r="H64">
+        <v>2</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -9205,12 +9166,17 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Left TKA</t>
+          <t>TKA (L)</t>
         </is>
       </c>
       <c r="K64">
         <v>0</v>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="M64" s="1">
         <v>45217</v>
       </c>
@@ -9219,7 +9185,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>check chart</t>
         </is>
       </c>
     </row>
@@ -9249,7 +9225,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G65">
@@ -9260,27 +9236,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>htn,osa</t>
+          <t>OSA,HTN</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>R Total knee</t>
+          <t>Right Total knee</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>unk</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>10/9/23</t>
         </is>
       </c>
       <c r="N65">
@@ -9288,7 +9264,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>11/6/24</t>
+          <t>November 6 2024</t>
         </is>
       </c>
       <c r="P65">
@@ -9316,23 +9292,21 @@
           <t>C0603</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>7/6/24</t>
-        </is>
-      </c>
-      <c r="E66">
-        <v>65</v>
+      <c r="D66" s="1">
+        <v>45479</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>65 yo</t>
+        </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>30.9 kg/m2</t>
-        </is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G66">
+        <v>30.9</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -9346,13 +9320,11 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>TKA (R)</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>1 day</t>
-        </is>
+          <t>Right Total knee</t>
+        </is>
+      </c>
+      <c r="K66">
+        <v>1</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -9367,13 +9339,16 @@
       <c r="N66">
         <v>40.5</v>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>2025-07-06</t>
-        </is>
+      <c r="O66" s="1">
+        <v>45844</v>
       </c>
       <c r="P66">
         <v>71.7</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>pt moved out of state</t>
+        </is>
       </c>
     </row>
     <row r="67">
